--- a/Our project/Ocean_Cleanup_Stakeholder_Matrix.xlsx
+++ b/Our project/Ocean_Cleanup_Stakeholder_Matrix.xlsx
@@ -1,22 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\candi\OneDrive\Documents\CIEM0000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/mpatrignani_tudelft_nl/Documents/SystemProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB769FE-FA16-48D6-93CA-5104B5446153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48A79E1E-604D-4BA7-9519-AB544569A543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="12468" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stakeholder Matrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Notes" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,7 +45,7 @@
     <author>tc={A76578B2-5470-4BF7-B80B-B4D795110382}</author>
   </authors>
   <commentList>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{77840A6B-36FE-4A0F-880E-FD0EE9717350}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{77840A6B-36FE-4A0F-880E-FD0EE9717350}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -36,7 +53,7 @@
     Recovery of the fish</t>
       </text>
     </comment>
-    <comment ref="F15" authorId="1" shapeId="0" xr:uid="{46288247-A8CD-4B93-8461-8EDC737BF405}">
+    <comment ref="F14" authorId="1" shapeId="0" xr:uid="{46288247-A8CD-4B93-8461-8EDC737BF405}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -44,7 +61,7 @@
     whether the concept is attractive and credible enough to justify continued funding as it scales — i.e., does scaling up make the story easier or harder to fund. </t>
       </text>
     </comment>
-    <comment ref="A20" authorId="2" shapeId="0" xr:uid="{A76578B2-5470-4BF7-B80B-B4D795110382}">
+    <comment ref="A18" authorId="2" shapeId="0" xr:uid="{A76578B2-5470-4BF7-B80B-B4D795110382}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Criteria</t>
   </si>
@@ -80,6 +97,9 @@
     <t>The Ocean Cleanup</t>
   </si>
   <si>
+    <t>Plastic removal efficiency (kg per time)</t>
+  </si>
+  <si>
     <t>Cost per kg removed</t>
   </si>
   <si>
@@ -92,28 +112,165 @@
     <t>North Pacific commercial fishers</t>
   </si>
   <si>
+    <t>Fishing ground access</t>
+  </si>
+  <si>
     <t>Gear conflict / entanglement risk</t>
   </si>
   <si>
-    <t>Fishing ground access</t>
-  </si>
-  <si>
     <t>Vessel traffic disruption</t>
   </si>
   <si>
     <t>Investors/donors</t>
   </si>
   <si>
+    <t>Ecological impact</t>
+  </si>
+  <si>
+    <t>Marine conservation advocates</t>
+  </si>
+  <si>
+    <t>Unintended ecological harm (bycatch risk)</t>
+  </si>
+  <si>
+    <t>Long-term ecosystem recovery</t>
+  </si>
+  <si>
+    <t>Citizens</t>
+  </si>
+  <si>
+    <t>Personal Health</t>
+  </si>
+  <si>
+    <t>Beach/coastal cleanliness benefit</t>
+  </si>
+  <si>
     <t>Ecological/bycatch risk</t>
   </si>
   <si>
-    <t>Net environmental benefit</t>
-  </si>
-  <si>
-    <t>Citizens</t>
-  </si>
-  <si>
-    <t>Beach/coastal cleanliness benefit</t>
+    <t>100= best outcome for stakeholder (low risk/low disruption)</t>
+  </si>
+  <si>
+    <t>0=worst outcome for stakeholders</t>
+  </si>
+  <si>
+    <t>* **The Ocean Cleanup**
+  * **Plastic removal effectiveness – 35%**
+    * Given the main purpose of the system is to remove plastic from the Great Pacific Garbage Patch, this is considered the most important criterion.
+    * **Modular Fleet – 65:** Distributed units can collect plastic across a broad area, but their smaller individual size may result in a lower collection capacity.
+    * **Anchored Barrier Array – 45:** The system depends on ocean currents carrying plastic towards a fixed location and therefore cannot actively follow areas of high plastic concentration.
+    * **Autonomous Skimmer Vessels – 75:** The vessels can actively target plastic hotspots, although the limited storage capacity of individual vessels restricts total collection.
+    * **System 03 – 90:** Specifically designed for large-scale plastic removal and able to actively target areas of high plastic concentration using towing vessels and environmental monitoring.
+  * **Cost effectiveness – 25%**
+    * Cost is important because the cleanup system must remain financially viable over long-term and large-scale operation.
+    * **Modular Fleet – 75:** Passive movement reduces propulsion costs, although maintaining and retrieving many individual units adds logistical costs.
+    * **Anchored Barrier Array – 80:** Mainly uses natural currents and requires little continuous propulsion, although installation and maintenance of deep-ocean moorings may be expensive.
+    * **Autonomous Skimmer Vessels – 55:** Requires energy, autonomous technology and maintenance for many individual vessels.
+    * **System 03 – 60:** Requires two vessels to continuously tow and operate the system, increasing fuel and operational costs.
+  * **Scalability – 20%**
+    * Large-scale deployment is necessary because of the very large area of the Great Pacific Garbage Patch.
+    * **Modular Fleet – 85:** Additional units can be added relatively easily, making the concept highly modular.
+    * **Anchored Barrier Array – 55:** Scaling requires installing additional anchoring and mooring systems in deep-ocean conditions.
+    * **Autonomous Skimmer Vessels – 80:** The fleet can be expanded by adding more vessels, although maintenance and coordination become increasingly complex.
+    * **System 03 – 70:** Larger or additional systems can be deployed, but each requires significant vessels, infrastructure and operational resources.
+  * **Ecological compatibility – 15%**
+    * The cleanup system should minimize unintended ecological disturbance while removing plastic.
+    * **Modular Fleet – 70:** Passive operation limits energy use, although many individual floating systems increase the number of structures interacting with marine life.
+    * **Anchored Barrier Array – 75:** Requires little propulsion and therefore has relatively low operational disturbance, although permanent moorings and structures may affect the marine environment.
+    * **Autonomous Skimmer Vessels – 65:** Active movement and repeated vessel operation may increase interactions with marine organisms.
+    * **System 03 – 65:** Large-scale active collection provides environmental benefits but the large barrier and towing operation may still interact with marine organisms.
+  * **Public visibility and awareness – 5%**
+    * Public visibility is useful for communicating impact and attracting support but is secondary to actual cleanup performance.
+    * **Modular Fleet – 55:** Multiple small systems may be less visually recognizable.
+    * **Anchored Barrier Array – 45:** A fixed offshore system has relatively low public visibility.
+    * **Autonomous Skimmer Vessels – 70:** Autonomous vessels provide an innovative and easily communicable concept.
+    * **System 03 – 90:** As a large operating cleanup system, System 03 provides a clear and visible demonstration of plastic removal.
+* **North Pacific Commercial Fishers**
+  * **Fishing-ground accessibility – 40%**
+    * Maintaining access to productive fishing areas is a major economic concern for fishers.
+    * **Modular Fleet – 60:** Many floating units may occupy fishing areas but individually require relatively little space.
+    * **Anchored Barrier Array – 40:** Permanently occupies specific locations and therefore presents the greatest potential restriction to fishing-ground access.
+    * **Autonomous Skimmer Vessels – 80:** Small mobile vessels can potentially move around fishing operations and avoid restricting access.
+    * **System 03 – 65:** The system is mobile rather than permanently occupying an area, although its large size can temporarily restrict access.
+  * **Compatibility with fishing gear – 35%**
+    * Damage or interference with fishing gear can create direct financial losses for fishing operators.
+    * **Modular Fleet – 55:** The large number of floating systems may create some risk of interaction with fishing equipment.
+    * **Anchored Barrier Array – 40:** Fixed barriers and mooring infrastructure may create significant potential for interaction with fishing gear.
+    * **Autonomous Skimmer Vessels – 80:** Small mobile vessels can potentially detect and avoid fishing equipment.
+    * **System 03 – 65:** Its large barrier may interact with fishing operations, although its active control allows some avoidance.
+  * **Low interference with vessel operations – 25%**
+    * Vessel traffic and navigation interference matter but are considered slightly less important than access and protection of fishing gear.
+    * **Modular Fleet – 75:** Requires relatively little supporting vessel activity after deployment.
+    * **Anchored Barrier Array – 90:** Once installed, relatively little continuous vessel traffic is required.
+    * **Autonomous Skimmer Vessels – 65:** A large fleet of small vessels could increase traffic in the operating area.
+    * **System 03 – 50:** Requires two towing vessels and a large 2.2 km system, producing the greatest direct interaction with other vessel operations.
+* **Investors / Donors**
+  * **Cost effectiveness – 40%**
+    * Funding should produce as much environmental impact as possible, making efficient use of available financial resources important.
+    * **Modular Fleet – 75:** Low propulsion requirements are beneficial, although maintaining many units may increase logistical costs.
+    * **Anchored Barrier Array – 80:** Passive operation reduces continuous energy costs, although installation and maintenance remain challenging.
+    * **Autonomous Skimmer Vessels – 50:** Energy, autonomous technology and fleet maintenance create significant costs.
+    * **System 03 – 60:** Demonstrated performance is attractive, but continuous operation of two vessels increases costs.
+  * **Scalability – 30%**
+    * Investors and donors are likely to value solutions whose environmental impact can be expanded over time.
+    * **Modular Fleet – 85:** Highly scalable because additional modules can be progressively added.
+    * **Anchored Barrier Array – 55:** Expansion requires additional fixed structures and deep-water anchoring.
+    * **Autonomous Skimmer Vessels – 80:** The fleet can grow by adding more vessels.
+    * **System 03 – 70:** Additional systems can be deployed, but each requires substantial infrastructure and vessel capacity.
+  * **Public visibility and demonstrable impact – 30%**
+    * Donors benefit from being able to clearly see and communicate the environmental impact created by their funding.
+    * **Modular Fleet – 60:** Provides visible action but individual systems are comparatively small.
+    * **Anchored Barrier Array – 45:** Fixed offshore infrastructure is less visible and its impact is more difficult to communicate.
+    * **Autonomous Skimmer Vessels – 75:** Innovative autonomous technology provides a visible and easily understandable concept.
+    * **System 03 – 95:** Provides the clearest large-scale and demonstrable example of active ocean cleanup.
+* **Marine Conservation Advocates**
+  * **Ecological compatibility – 40%**
+    * Avoiding harm to marine ecosystems is one of the main priorities for conservation stakeholders.
+    * **Modular Fleet – 70:** Passive operation limits disturbance, although a large number of floating devices increases interactions with marine organisms.
+    * **Anchored Barrier Array – 75:** Requires little active propulsion but permanent structures and anchoring can still affect the marine environment.
+    * **Autonomous Skimmer Vessels – 65:** Active vessel movement may produce more interaction with marine organisms.
+    * **System 03 – 65:** Large-scale collection has ecological benefits but the large barrier and continuous towing may create some ecological disturbance.
+  * **Net environmental benefit – 40%**
+    * Conservation stakeholders care not only about minimizing harm but also about achieving meaningful plastic removal.
+    * **Modular Fleet – 65:** Provides useful plastic removal but may have lower collection capacity than larger active systems.
+    * **Anchored Barrier Array – 50:** Limited ability to follow changing plastic concentrations reduces overall environmental effectiveness.
+    * **Autonomous Skimmer Vessels – 70:** Can target plastic hotspots and adapt to changing conditions.
+    * **System 03 – 90:** Designed specifically for large-scale plastic removal and active hotspot targeting.
+  * **Monitoring and data-generation capability – 20%**
+    * Environmental monitoring is valuable for understanding plastic distribution and evaluating ecological effects, but remains secondary to direct environmental performance.
+    * **Modular Fleet – 55:** Monitoring equipment could be added, but it is not an inherent strength of the concept.
+    * **Anchored Barrier Array – 50:** Can collect data at fixed locations but has limited spatial coverage.
+    * **Autonomous Skimmer Vessels – 80:** A moving distributed fleet could potentially gather data across a large area.
+    * **System 03 – 85:** Already incorporates environmental monitoring and AI modelling to identify high-density plastic areas.
+* **Citizens**
+  * **Contribution to reducing ocean plastic – 45%**
+    * The most direct societal benefit of these systems is the removal of accumulated ocean plastic.
+    * **Modular Fleet – 65:** Provides distributed cleanup but potentially has lower individual collection capacity.
+    * **Anchored Barrier Array – 45:** Limited by its fixed position and dependence on currents transporting plastic towards it.
+    * **Autonomous Skimmer Vessels – 75:** Can move towards areas with greater plastic concentrations.
+    * **System 03 – 90:** Specifically designed for large-scale removal of accumulated plastic from the Great Pacific Garbage Patch.
+  * **Perceived environmental benefit / cleanliness – 30%**
+    * Citizens are likely to value visible improvements in marine environmental quality, although the direct effect on beaches is outside the main system boundary.
+    * **Modular Fleet – 60:** Provides moderate visible environmental improvement.
+    * **Anchored Barrier Array – 45:** Lower collection effectiveness reduces perceived overall environmental impact.
+    * **Autonomous Skimmer Vessels – 70:** Flexible targeted operation provides relatively clear environmental benefits.
+    * **System 03 – 80:** Large-scale collection creates the strongest visible contribution to improving ocean cleanliness.
+  * **Ecological compatibility – 25%**
+    * Citizens may prefer cleanup systems that do not solve plastic pollution by creating significant additional environmental impacts.
+    * **Modular Fleet – 70:** Passive operation limits energy use but requires many individual floating systems.
+    * **Anchored Barrier Array – 75:** Low propulsion requirements are beneficial, although permanent anchoring may create local ecological effects.
+    * **Autonomous Skimmer Vessels – 65:** Active vessels require energy and may interact with marine organisms.
+    * **System 03 – 65:** Provides strong cleanup benefits but its large barrier and vessel operation may create additional ecological interactions.
+* **General scoring approach**
+  * All criteria are formulated so that a **higher score represents better performance from the stakeholder's perspective**.
+  * Scores are relative qualitative estimates rather than directly measured quantitative values.
+  * The scores are based on the characteristics and trade-offs identified during the alternatives exploration.
+  * The 0–100 scale allows qualitative differences between alternatives to be incorporated into the MCDA while maintaining a consistent direction of preference.
+  * Weightings are assigned according to the relative importance of each criterion to the stakeholder and sum to 100% within each stakeholder group.
+  * Rounded weights and scores are used to avoid suggesting a level of numerical precision that is not supported by the available information.</t>
+  </si>
+  <si>
+    <t>F17</t>
   </si>
   <si>
     <t>Notes</t>
@@ -129,34 +286,13 @@
   </si>
   <si>
     <t>- Added 'System 03 (current)' as a baseline alternative alongside the four proposed alternatives; its scores are illustrative placeholders reflecting its known real-world profile (high removal efficiency and public visibility, moderate cost-effectiveness) — replace with real data.</t>
-  </si>
-  <si>
-    <t>Plastic removal efficiency (kg per time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scalability </t>
-  </si>
-  <si>
-    <t>Monitoring</t>
-  </si>
-  <si>
-    <t>Public awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public awareness </t>
-  </si>
-  <si>
-    <t>Marine conservation advocates</t>
-  </si>
-  <si>
-    <t>Plastic removal efficiency (health)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,12 +332,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -211,6 +341,24 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -248,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -270,18 +418,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,13 +743,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A8" dT="2026-09-09T14:39:31.59" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{77840A6B-36FE-4A0F-880E-FD0EE9717350}">
+  <threadedComment ref="A7" dT="2026-09-09T14:39:31.59" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{77840A6B-36FE-4A0F-880E-FD0EE9717350}">
     <text>Recovery of the fish</text>
   </threadedComment>
-  <threadedComment ref="F15" dT="2026-09-09T14:19:44.89" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{46288247-A8CD-4B93-8461-8EDC737BF405}">
+  <threadedComment ref="F14" dT="2026-09-09T14:19:44.89" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{46288247-A8CD-4B93-8461-8EDC737BF405}">
     <text xml:space="preserve">whether the concept is attractive and credible enough to justify continued funding as it scales — i.e., does scaling up make the story easier or harder to fund. </text>
   </threadedComment>
-  <threadedComment ref="A20" dT="2026-09-09T14:29:26.42" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{A76578B2-5470-4BF7-B80B-B4D795110382}">
+  <threadedComment ref="A18" dT="2026-09-09T14:29:26.42" personId="{86DBFB6E-C3C6-456A-A9EC-32CADF6BF1C0}" id="{A76578B2-5470-4BF7-B80B-B4D795110382}">
     <text>Add that the amount of plastic is directly related to the health</text>
   </threadedComment>
 </ThreadedComments>
@@ -604,27 +757,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="19.899999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -634,7 +787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -644,58 +797,58 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C3" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" s="4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E3" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F3" s="6">
         <v>0.35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C4" s="4">
         <v>80</v>
       </c>
       <c r="D4" s="4">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F4" s="6">
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4">
+        <v>85</v>
+      </c>
+      <c r="C5" s="4">
+        <v>55</v>
+      </c>
+      <c r="D5" s="4">
         <v>80</v>
-      </c>
-      <c r="C5" s="4">
-        <v>50</v>
-      </c>
-      <c r="D5" s="4">
-        <v>60</v>
       </c>
       <c r="E5" s="4">
         <v>70</v>
@@ -704,336 +857,306 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4">
+        <v>70</v>
+      </c>
+      <c r="C6" s="4">
+        <v>75</v>
+      </c>
+      <c r="D6" s="4">
+        <v>65</v>
+      </c>
+      <c r="E6" s="4">
+        <v>65</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4">
         <v>60</v>
       </c>
-      <c r="C6" s="4">
-        <v>70</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C8" s="4">
         <v>40</v>
       </c>
-      <c r="E6" s="4">
-        <v>70</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="4">
-        <v>50</v>
-      </c>
-      <c r="C7" s="4">
-        <v>50</v>
-      </c>
-      <c r="D7" s="4">
-        <v>50</v>
-      </c>
-      <c r="E7" s="4">
-        <v>50</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="4">
+        <v>80</v>
+      </c>
+      <c r="E8" s="4">
+        <v>65</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D9" s="4">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E9" s="4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F9" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D10" s="4">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E10" s="4">
         <v>50</v>
       </c>
       <c r="F10" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4">
+        <v>60</v>
+      </c>
+      <c r="C12" s="4">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4">
+        <v>75</v>
+      </c>
+      <c r="E12" s="4">
+        <v>95</v>
+      </c>
+      <c r="F12" s="6">
         <v>0.35</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4">
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4">
+        <v>75</v>
+      </c>
+      <c r="C13" s="4">
+        <v>80</v>
+      </c>
+      <c r="D13" s="4">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4">
         <v>60</v>
       </c>
-      <c r="C11" s="4">
+      <c r="F13" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4">
+        <v>85</v>
+      </c>
+      <c r="C14" s="4">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4">
         <v>80</v>
       </c>
-      <c r="D11" s="4">
-        <v>30</v>
-      </c>
-      <c r="E11" s="4">
-        <v>60</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="E14" s="4">
         <v>70</v>
       </c>
-      <c r="C13" s="4">
-        <v>40</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="F14" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="4">
+        <v>70</v>
+      </c>
+      <c r="C16" s="4">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4">
+        <v>65</v>
+      </c>
+      <c r="E16" s="4">
+        <v>65</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="4">
+        <v>65</v>
+      </c>
+      <c r="C17" s="4">
+        <v>50</v>
+      </c>
+      <c r="D17" s="4">
+        <v>70</v>
+      </c>
+      <c r="E17" s="4">
         <v>90</v>
       </c>
-      <c r="E13" s="4">
-        <v>85</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4">
-        <v>50</v>
-      </c>
-      <c r="C14" s="4">
-        <v>70</v>
-      </c>
-      <c r="D14" s="4">
-        <v>30</v>
-      </c>
-      <c r="E14" s="4">
-        <v>60</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="4">
-        <v>80</v>
-      </c>
-      <c r="C15" s="4">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4">
-        <v>60</v>
-      </c>
-      <c r="E15" s="4">
-        <v>80</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4">
-        <v>60</v>
-      </c>
-      <c r="C17" s="4">
-        <v>70</v>
-      </c>
-      <c r="D17" s="4">
-        <v>40</v>
-      </c>
-      <c r="E17" s="4">
-        <v>65</v>
-      </c>
       <c r="F17" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4">
-        <v>70</v>
-      </c>
-      <c r="C18" s="4">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4">
-        <v>50</v>
-      </c>
-      <c r="E18" s="4">
-        <v>75</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <v>60</v>
       </c>
       <c r="C19" s="4">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D19" s="4">
         <v>70</v>
       </c>
       <c r="E19" s="4">
+        <v>80</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4">
+        <v>65</v>
+      </c>
+      <c r="C20" s="4">
+        <v>45</v>
+      </c>
+      <c r="D20" s="4">
         <v>75</v>
       </c>
-      <c r="F19" s="6">
+      <c r="E20" s="4">
+        <v>90</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>70</v>
+      </c>
+      <c r="C21" s="4">
+        <v>75</v>
+      </c>
+      <c r="D21" s="4">
+        <v>65</v>
+      </c>
+      <c r="E21" s="4">
+        <v>65</v>
+      </c>
+      <c r="F21" s="6">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4">
-        <v>50</v>
-      </c>
-      <c r="C21" s="4">
-        <v>50</v>
-      </c>
-      <c r="D21" s="4">
-        <v>40</v>
-      </c>
-      <c r="E21" s="4">
-        <v>55</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="4">
-        <v>70</v>
-      </c>
-      <c r="C22" s="4">
-        <v>40</v>
-      </c>
-      <c r="D22" s="4">
-        <v>90</v>
-      </c>
-      <c r="E22" s="4">
-        <v>90</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="4">
-        <v>50</v>
-      </c>
-      <c r="C23" s="4">
-        <v>70</v>
-      </c>
-      <c r="D23" s="4">
-        <v>30</v>
-      </c>
-      <c r="E23" s="4">
-        <v>65</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15"/>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15"/>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="5"/>
     </row>
   </sheetData>
@@ -1044,36 +1167,56 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797F5CE0-1200-49A2-9A05-DCAACA981454}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="409.6">
+      <c r="A1" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.6">
       <c r="A1" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
